--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,889 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128749574</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>611971</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6969234</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128750644</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>611884</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6969442</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128750510</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>611986</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6969419</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128749877</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>611872</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6969431</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128750444</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>612018</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6969469</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128749866</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>611863</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6969422</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128749678</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>611933</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6969333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128750423</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>611990</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6969460</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128749943</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98508</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Vällingmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>611874</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6969481</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128750423</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98542</v>
+        <v>98549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128750423</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128750423</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128750423</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128749574</v>
       </c>
       <c r="B4" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128750644</v>
       </c>
       <c r="B5" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128750510</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128750444</v>
       </c>
       <c r="B8" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128749866</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128749678</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128750423</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111363062</v>
+        <v>111363063</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611993.5825821182</v>
+        <v>611971</v>
       </c>
       <c r="R2" t="n">
-        <v>6969303.448465708</v>
+        <v>6969329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111363063</v>
+        <v>111363062</v>
       </c>
       <c r="B3" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611971.1816591223</v>
+        <v>611993</v>
       </c>
       <c r="R3" t="n">
-        <v>6969329.20390647</v>
+        <v>6969304</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128749574</v>
+        <v>128749678</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611971</v>
+        <v>611933</v>
       </c>
       <c r="R4" t="n">
-        <v>6969234</v>
+        <v>6969333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128750644</v>
+        <v>128749574</v>
       </c>
       <c r="B5" t="n">
-        <v>92242</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611884</v>
+        <v>611971</v>
       </c>
       <c r="R5" t="n">
-        <v>6969442</v>
+        <v>6969234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128750510</v>
+        <v>128749866</v>
       </c>
       <c r="B6" t="n">
-        <v>91506</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611986</v>
+        <v>611863</v>
       </c>
       <c r="R6" t="n">
-        <v>6969419</v>
+        <v>6969422</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1163,7 @@
         <v>128749877</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128750444</v>
+        <v>128750644</v>
       </c>
       <c r="B8" t="n">
-        <v>80181</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612018</v>
+        <v>611884</v>
       </c>
       <c r="R8" t="n">
-        <v>6969469</v>
+        <v>6969442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128749866</v>
+        <v>128750510</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611863</v>
+        <v>611986</v>
       </c>
       <c r="R9" t="n">
-        <v>6969422</v>
+        <v>6969419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,27 +1451,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128749678</v>
+        <v>128750444</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1516,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611933</v>
+        <v>612018</v>
       </c>
       <c r="R10" t="n">
-        <v>6969333</v>
+        <v>6969469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1551,7 @@
         <v>128750423</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1658,7 @@
         <v>128749943</v>
       </c>
       <c r="B12" t="n">
-        <v>98595</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22204-2025 artfynd.xlsx
+++ b/artfynd/A 22204-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111363063</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111363062</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749866</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749877</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750644</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750510</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128750423</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,8 +1804,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128749943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>